--- a/SGC-CKN/Excel/ba2a1c60-daef-4f2a-a69f-edbef53e1739_Cọc_thí_nghiệm_TP-02_TP-2_1200_14-03-2024.xlsx
+++ b/SGC-CKN/Excel/ba2a1c60-daef-4f2a-a69f-edbef53e1739_Cọc_thí_nghiệm_TP-02_TP-2_1200_14-03-2024.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>11:00 13/03/2024</t>
+    <t>11:00 13/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>10:15 14/03/2024</t>
+    <t>10:15 14/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">11:00
-13/03/2024</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:05
-13/03/2024</t>
+13/03/2026</t>
   </si>
   <si>
     <t>Thời gian phân bổ theo các mốc chính trên biên bản</t>
@@ -125,7 +125,7 @@
   </si>
   <si>
     <t xml:space="preserve">17:15
-13/03/2024</t>
+13/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -135,7 +135,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:40
-13/03/2024</t>
+13/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -145,7 +145,7 @@
   </si>
   <si>
     <t xml:space="preserve">08:23
-14/03/2024</t>
+13/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -155,7 +155,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:15
-14/03/2024</t>
+13/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
